--- a/data/saida/Documento_Inventario.xlsx
+++ b/data/saida/Documento_Inventario.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AE$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AE$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -51,11 +53,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AE101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -437,9 +441,9 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="5" customWidth="1" min="19" max="19"/>
@@ -454,168 +458,9243 @@
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="19" customWidth="1" min="29" max="29"/>
     <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>material</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>descricao_material</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>lote</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>tipo_estoque</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>posicao</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>deposito</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>tipo_deposito</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>area_armazenagem</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>unidade_medida</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>estoque_disponivel</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>estoque_para_armazenar</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>estoque_saida</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>estoque_total</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>data_entrada</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>data_vencimento</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>ultimo_movimento</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>unidade_deposito</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>ordem_transporte</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>rua</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>nivel</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>numero_posicao</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>especial</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>prioridade_posicao</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>sufixo</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>documento_inventario</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>data_contagem</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>quantidade_sistema</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>quantidade_contada</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>dias_sem_contagem</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>custo_unitario</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>valor_lote</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3001628</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2600014414</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EBI447</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>600</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>600</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>46158</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>47149</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1024542898</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2003203869</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>EBI</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>47</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>27960</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3001628</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2600014414</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EBI449</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>700</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>700</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>46158</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>47149</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1024542896</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2003203866</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>EBI</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>49</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>32620</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3001628</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2600014414</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EBI250</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>300</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>300</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>46158</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>47149</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1024542897</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2003228587</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>EBI</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>50</v>
+      </c>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>13980</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>EBM101</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>750</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>750</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>46167</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1024582758</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2003213255</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EBM107</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1024575077</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2003202086</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>EBM112</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1024575071</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2003202082</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
+      </c>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EBM115</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1024575061</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2003202356</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>15</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EBM120</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1024575070</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2003202079</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>EBM122</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1024575062</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2003202080</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>22</v>
+      </c>
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>EBM124</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1024575078</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2003202083</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24</v>
+      </c>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>EBM126</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1024575074</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2003202101</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>26</v>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EBM128</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1024575068</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2003202077</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>28</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EBM130</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1024575055</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2003203670</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>30</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EBM133</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1024575056</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2003203648</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>33</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>EBN3W2</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>500</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>500</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1024549996</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2003191745</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EBN3W1</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1024465740</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EBN400</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1024465744</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EBN500</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1024465735</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EBN303</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>59.997</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>59.997</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>46196</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1024465733</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2003257391</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2666.26668</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EBN105</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1024575054</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2003203767</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EBN306</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1024465724</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EBN507</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1024465749</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>EBN408</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1024465736</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>EBN309</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>500</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>500</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1024549994</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2003191747</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>9</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>EBN510</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1024465741</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>10</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>EBN311</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1024465751</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>11</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EBN116</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1024575069</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2003202078</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>16</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>EBN316</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1024465752</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>16</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>EBN117</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1024575076</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2003202088</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>17</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>EBN417</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1024465748</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>17</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>EBN418</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1024465756</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>18</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>EBN419</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1024465746</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>19</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>EBN120</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1024575075</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2003202099</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>20</v>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EBN420</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1024465754</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>20</v>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>EBN421</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1024465739</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>21</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>EBN322</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1024465747</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>22</v>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>EBN422</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1024465742</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>22</v>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>EBN423</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1024465728</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>23</v>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>EBN425</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1024465743</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>25</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>EBN326</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>500</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>500</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1024549993</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2003191757</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>26</v>
+      </c>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>EBN127</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1024575065</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2003202120</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>27</v>
+      </c>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>EBN327</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>500</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>500</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1024549998</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2003191751</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>27</v>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>EBN427</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1024465734</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>27</v>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>EBN333</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1024465726</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>33</v>
+      </c>
+      <c r="V45" t="b">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>EBN134</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1024575058</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2003202108</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>34</v>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>EBN434</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1024465727</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>34</v>
+      </c>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>EBN436</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>139.993</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>139.993</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>46206</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1024465767</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2003274184</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>36</v>
+      </c>
+      <c r="V48" t="b">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>6221.288919999999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>EBN538</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1024465755</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>38</v>
+      </c>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>EBN440</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1024465745</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>40</v>
+      </c>
+      <c r="V50" t="b">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>EBN442</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1024465765</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>42</v>
+      </c>
+      <c r="V51" t="b">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>EBN443</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1024465750</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>43</v>
+      </c>
+      <c r="V52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>EBN444</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1024465757</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>44</v>
+      </c>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EBN345</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1024465732</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>45</v>
+      </c>
+      <c r="V54" t="b">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EBN447</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1024465731</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>47</v>
+      </c>
+      <c r="V55" t="b">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EBN449</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1024465763</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>49</v>
+      </c>
+      <c r="V56" t="b">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>EBN553</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1024465730</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>53</v>
+      </c>
+      <c r="V57" t="b">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>EBN156</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>999.152</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>999.152</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1024575063</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2003216281</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>56</v>
+      </c>
+      <c r="V58" t="b">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>12325.4391568</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>EBN559</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1024465738</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>59</v>
+      </c>
+      <c r="V59" t="b">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>EBO1W1</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1024575072</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2003202107</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V60" t="b">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>EBO401</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>500</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>500</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1024549988</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2003191766</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="b">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>EBO303</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>500</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>500</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1024549992</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2003191762</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
+      </c>
+      <c r="V62" t="b">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>EBO109</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1024575066</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2003202074</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>9</v>
+      </c>
+      <c r="V63" t="b">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>EBO517</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>500</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>500</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1024549997</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2003191772</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>17</v>
+      </c>
+      <c r="V64" t="b">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>EBO118</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>750</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>750</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>46167</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1024582759</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2003213267</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>18</v>
+      </c>
+      <c r="V65" t="b">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>EBO519</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>500</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>500</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1024549991</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2003191779</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>19</v>
+      </c>
+      <c r="V66" t="b">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>EBO120</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1024575067</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2003202076</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>20</v>
+      </c>
+      <c r="V67" t="b">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>EBO520</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>300</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>300</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1024549999</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2003191794</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>20</v>
+      </c>
+      <c r="V68" t="b">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>13332</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>EBO521</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>500</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>500</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1024549989</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2003191795</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>21</v>
+      </c>
+      <c r="V69" t="b">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>EBO522</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>500</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>500</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1024549995</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2003191801</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>22</v>
+      </c>
+      <c r="V70" t="b">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>EBO523</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>500</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>500</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1024549990</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2003191802</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>23</v>
+      </c>
+      <c r="V71" t="b">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>EBO141</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>750</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>750</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1024582763</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2003213762</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>41</v>
+      </c>
+      <c r="V72" t="b">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>EBO347</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1024465729</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>47</v>
+      </c>
+      <c r="V73" t="b">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>EBO348</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1024465764</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>48</v>
+      </c>
+      <c r="V74" t="b">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>EBP3W3</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1024465725</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V75" t="b">
+        <v>1</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>EBP402</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1024465771</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
+      </c>
+      <c r="V76" t="b">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>EBP303</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1024465772</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3</v>
+      </c>
+      <c r="V77" t="b">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>EBP106</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1024575073</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2003202105</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>6</v>
+      </c>
+      <c r="V78" t="b">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EBP119</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1024575057</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2003202428</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>19</v>
+      </c>
+      <c r="V79" t="b">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>EBP122</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1024575059</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2003202399</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>22</v>
+      </c>
+      <c r="V80" t="b">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>EBP322</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1024465753</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>22</v>
+      </c>
+      <c r="V81" t="b">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>EBP123</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1024575060</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2003202396</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>23</v>
+      </c>
+      <c r="V82" t="b">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>EBP327</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1024465766</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T83" t="n">
+        <v>3</v>
+      </c>
+      <c r="U83" t="n">
+        <v>27</v>
+      </c>
+      <c r="V83" t="b">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>EBR4W4</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1024465758</v>
+      </c>
+      <c r="R84" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V84" t="b">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>EBR413</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1024465737</v>
+      </c>
+      <c r="R85" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
+      </c>
+      <c r="T85" t="n">
+        <v>4</v>
+      </c>
+      <c r="U85" t="n">
+        <v>13</v>
+      </c>
+      <c r="V85" t="b">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>EBS2W1</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>250</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>250</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1024582771</v>
+      </c>
+      <c r="R86" t="n">
+        <v>2003213738</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V86" t="b">
+        <v>1</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>5629.4725</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>EBS102</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>750</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>750</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1024582756</v>
+      </c>
+      <c r="R87" t="n">
+        <v>2003205909</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" t="n">
+        <v>2</v>
+      </c>
+      <c r="V87" t="b">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>EBS106</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>750</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>750</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1024582757</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2003213734</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>6</v>
+      </c>
+      <c r="V88" t="b">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>EBS109</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1024575064</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2003202265</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
+        <v>9</v>
+      </c>
+      <c r="V89" t="b">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>EBS114</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>750</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>750</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1024582754</v>
+      </c>
+      <c r="R90" t="n">
+        <v>2003213735</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T90" t="n">
+        <v>1</v>
+      </c>
+      <c r="U90" t="n">
+        <v>14</v>
+      </c>
+      <c r="V90" t="b">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>EBS115</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>750</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>750</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1024582755</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2003213737</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>15</v>
+      </c>
+      <c r="V91" t="b">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>EBS116</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>750</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>750</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1024582770</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2003213736</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>16</v>
+      </c>
+      <c r="V92" t="b">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>EBS117</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>750</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>750</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1024582762</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2003213740</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>17</v>
+      </c>
+      <c r="V93" t="b">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>EBS118</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>750</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>750</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P94" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1024582767</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2003213739</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>18</v>
+      </c>
+      <c r="V94" t="b">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>EBS119</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>750</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>750</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P95" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1024582761</v>
+      </c>
+      <c r="R95" t="n">
+        <v>2003213743</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" t="n">
+        <v>19</v>
+      </c>
+      <c r="V95" t="b">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>EBS120</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>750</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>750</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1024582766</v>
+      </c>
+      <c r="R96" t="n">
+        <v>2003213744</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T96" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" t="n">
+        <v>20</v>
+      </c>
+      <c r="V96" t="b">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>EBS121</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>750</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>750</v>
+      </c>
+      <c r="N97" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P97" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1024582769</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2003213745</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>21</v>
+      </c>
+      <c r="V97" t="b">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>EBS122</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>750</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>750</v>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1024582768</v>
+      </c>
+      <c r="R98" t="n">
+        <v>2003213747</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="n">
+        <v>22</v>
+      </c>
+      <c r="V98" t="b">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>EBS123</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>750</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>750</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1024582764</v>
+      </c>
+      <c r="R99" t="n">
+        <v>2003213760</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>23</v>
+      </c>
+      <c r="V99" t="b">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>EBS124</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>750</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>750</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1024582760</v>
+      </c>
+      <c r="R100" t="n">
+        <v>2003213746</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T100" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" t="n">
+        <v>24</v>
+      </c>
+      <c r="V100" t="b">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>EBS125</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>750</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>750</v>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P101" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1024582765</v>
+      </c>
+      <c r="R101" t="n">
+        <v>2003213761</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
+        <v>25</v>
+      </c>
+      <c r="V101" t="b">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE1"/>
+  <autoFilter ref="A1:AE101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/saida/Documento_Inventario.xlsx
+++ b/data/saida/Documento_Inventario.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AE$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AE$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -457,8 +457,8 @@
     <col width="20" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="19" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -620,21 +620,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3000413</v>
+        <v>3001628</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESTEARATO DE MAGNESIO GRAU FARMACEUTICO</t>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2600012791</t>
+          <t>2600014414</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EBN446</t>
+          <t>EBI447</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -647,16 +647,16 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>125</v>
+        <v>600</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -665,33 +665,33 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>125</v>
+        <v>600</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>47603</v>
+        <v>47149</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>46206</v>
+        <v>46161</v>
       </c>
       <c r="Q2" t="n">
-        <v>1024505005</v>
+        <v>1024542898</v>
       </c>
       <c r="R2" t="n">
-        <v>2003274587</v>
+        <v>2003203869</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EBN</t>
+          <t>EBI</t>
         </is>
       </c>
       <c r="T2" t="n">
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" t="b">
         <v>0</v>
@@ -700,29 +700,29 @@
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>32.16031</v>
+        <v>46.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>4020.03875</v>
+        <v>27960</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3001786</v>
+        <v>3001628</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SORBITOL P 60 W (AL)</t>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2600014539</t>
+          <t>2600014414</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EBN356</t>
+          <t>EBI449</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -735,16 +735,16 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -753,33 +753,33 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>46169</v>
+        <v>46158</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>47815</v>
+        <v>47149</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>46200</v>
+        <v>46161</v>
       </c>
       <c r="Q3" t="n">
-        <v>1024544742</v>
+        <v>1024542896</v>
       </c>
       <c r="R3" t="n">
-        <v>2003265375</v>
+        <v>2003203866</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>EBN</t>
+          <t>EBI</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -788,29 +788,29 @@
         <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.19</v>
+        <v>46.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>1919</v>
+        <v>32620</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3001750</v>
+        <v>3001628</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA REFINADO</t>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2600013712</t>
+          <t>2600014414</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EBO227</t>
+          <t>EBI250</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -823,16 +823,16 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>359.714</v>
+        <v>300</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -841,33 +841,33 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>359.714</v>
+        <v>300</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>46142</v>
+        <v>46158</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>46383</v>
+        <v>47149</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>46192</v>
+        <v>46175</v>
       </c>
       <c r="Q4" t="n">
-        <v>1024526194</v>
+        <v>1024542897</v>
       </c>
       <c r="R4" t="n">
-        <v>2003252004</v>
+        <v>2003228587</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>EBI</t>
         </is>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="V4" t="b">
         <v>0</v>
@@ -876,29 +876,34 @@
         <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.23</v>
+        <v>46.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>2960.44622</v>
+        <v>13980</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3002259</v>
+        <v>3000550</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CARVAO VEGETAL GRAU FARMACEUTICO</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2600013442</t>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EBO451</t>
+          <t>EBM101</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -920,7 +925,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14.999</v>
+        <v>750</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -929,33 +934,33 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>14.999</v>
+        <v>750</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>47149</v>
+        <v>47460</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="Q5" t="n">
-        <v>1024521836</v>
+        <v>1024582758</v>
       </c>
       <c r="R5" t="n">
-        <v>2003208194</v>
+        <v>2003213255</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -964,29 +969,34 @@
         <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>187.9</v>
+        <v>22.51789</v>
       </c>
       <c r="AE5" t="n">
-        <v>2818.3121</v>
+        <v>16888.4175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3000530</v>
+        <v>3000366</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CITRATO SODIO DIHID GRAU FARMA</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2600006103</t>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EBP311</t>
+          <t>EBM107</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1008,7 +1018,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1017,33 +1027,33 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>46084</v>
+        <v>46160</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>47832</v>
+        <v>46886</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>46199</v>
+        <v>46160</v>
       </c>
       <c r="Q6" t="n">
-        <v>1024329254</v>
+        <v>1024575077</v>
       </c>
       <c r="R6" t="n">
-        <v>2003264063</v>
+        <v>2003202086</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>EBP</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -1052,29 +1062,34 @@
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.63923</v>
+        <v>12.3359</v>
       </c>
       <c r="AE6" t="n">
-        <v>481.9615</v>
+        <v>12335.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3000530</v>
+        <v>3000366</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CITRATO SODIO DIHID GRAU FARMA</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2600006103</t>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EBP411</t>
+          <t>EBM112</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1096,7 +1111,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>225</v>
+        <v>1000</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1105,33 +1120,33 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>225</v>
+        <v>1000</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46084</v>
+        <v>46160</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>47832</v>
+        <v>46886</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>46198</v>
+        <v>46160</v>
       </c>
       <c r="Q7" t="n">
-        <v>1024329253</v>
+        <v>1024575071</v>
       </c>
       <c r="R7" t="n">
-        <v>2003260086</v>
+        <v>2003202082</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>EBP</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V7" t="b">
         <v>0</v>
@@ -1140,29 +1155,34 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>9.63923</v>
+        <v>12.3359</v>
       </c>
       <c r="AE7" t="n">
-        <v>2168.82675</v>
+        <v>12335.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3001750</v>
+        <v>3000366</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA REFINADO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2600013712</t>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EBP112</t>
+          <t>EBM115</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1184,7 +1204,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>169.5</v>
+        <v>1000</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1193,33 +1213,33 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>169.5</v>
+        <v>1000</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>46142</v>
+        <v>46160</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>46383</v>
+        <v>46886</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>46197</v>
+        <v>46160</v>
       </c>
       <c r="Q8" t="n">
-        <v>1024740362</v>
+        <v>1024575061</v>
       </c>
       <c r="R8" t="n">
-        <v>2003259097</v>
+        <v>2003202356</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>EBP</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1228,29 +1248,34 @@
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>8.23</v>
+        <v>12.3359</v>
       </c>
       <c r="AE8" t="n">
-        <v>1394.985</v>
+        <v>12335.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3000539</v>
+        <v>3000366</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SORBITOL (SOL A 70%)</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2600012780</t>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EBP260</t>
+          <t>EBM120</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1272,7 +1297,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>164.9</v>
+        <v>1000</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1281,33 +1306,33 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>164.9</v>
+        <v>1000</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>47568</v>
+        <v>46886</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>46205</v>
+        <v>46160</v>
       </c>
       <c r="Q9" t="n">
-        <v>1024771133</v>
+        <v>1024575070</v>
       </c>
       <c r="R9" t="n">
-        <v>2003272273</v>
+        <v>2003202079</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>EBP</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
@@ -1316,29 +1341,34 @@
         <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.08061</v>
+        <v>12.3359</v>
       </c>
       <c r="AE9" t="n">
-        <v>1497.392589</v>
+        <v>12335.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3000514</v>
+        <v>3000366</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SACARINA SODICA DI-HIDRATADA</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2600010742</t>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EBQ326</t>
+          <t>EBM122</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1360,7 +1390,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>49.998</v>
+        <v>1000</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1369,33 +1399,33 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>49.998</v>
+        <v>1000</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>46129</v>
+        <v>46160</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>47709</v>
+        <v>46886</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>46175</v>
+        <v>46160</v>
       </c>
       <c r="Q10" t="n">
-        <v>1024455084</v>
+        <v>1024575062</v>
       </c>
       <c r="R10" t="n">
-        <v>2003227399</v>
+        <v>2003202080</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>EBQ</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
@@ -1404,29 +1434,34 @@
         <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>61.30117</v>
+        <v>12.3359</v>
       </c>
       <c r="AE10" t="n">
-        <v>3064.93589766</v>
+        <v>12335.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3001722</v>
+        <v>3000366</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AROMA DE CRANBERRY (AL)</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2600008927</t>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EBQ327</t>
+          <t>EBM124</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1448,7 +1483,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14.999</v>
+        <v>1000</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1457,30 +1492,33 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>14.999</v>
+        <v>1000</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>46160</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>46451</v>
+        <v>46886</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>46205</v>
+        <v>46160</v>
       </c>
       <c r="Q11" t="n">
-        <v>1024402877</v>
+        <v>1024575078</v>
       </c>
       <c r="R11" t="n">
-        <v>2003272279</v>
+        <v>2003202083</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>EBQ</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
@@ -1489,29 +1527,34 @@
         <v>1</v>
       </c>
       <c r="AD11" t="n">
-        <v>95.84</v>
+        <v>12.3359</v>
       </c>
       <c r="AE11" t="n">
-        <v>1437.50416</v>
+        <v>12335.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3003808</v>
+        <v>3000366</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ESSENCIA DE FRAMBOESA TKD</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2600016580</t>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>INF137</t>
+          <t>EBM126</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1524,7 +1567,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1533,7 +1576,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3.51</v>
+        <v>1000</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1542,33 +1585,33 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.51</v>
+        <v>1000</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>46487</v>
+        <v>46886</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>46202</v>
+        <v>46160</v>
       </c>
       <c r="Q12" t="n">
-        <v>1024760691</v>
+        <v>1024575074</v>
       </c>
       <c r="R12" t="n">
-        <v>2003268085</v>
+        <v>2003202101</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>INF</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
@@ -1577,24 +1620,24 @@
         <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>668.05</v>
+        <v>12.3359</v>
       </c>
       <c r="AE12" t="n">
-        <v>2344.8555</v>
+        <v>12335.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3000055</v>
+        <v>3000366</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALCOOL ETILICO GRAU FARMACEUTICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2600013125</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1604,7 +1647,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>INF245</t>
+          <t>EBM128</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1617,7 +1660,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1626,7 +1669,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>319.574</v>
+        <v>1000</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1635,49 +1678,8023 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>319.574</v>
+        <v>1000</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>47223</v>
+        <v>46886</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>46142</v>
+        <v>46160</v>
       </c>
       <c r="Q13" t="n">
-        <v>1024514056</v>
+        <v>1024575068</v>
       </c>
       <c r="R13" t="n">
-        <v>2003179337</v>
+        <v>2003202077</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>INF</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>28</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EBM130</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1024575055</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2003203670</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>30</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EBM133</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1024575056</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2003203648</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>EBM</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>33</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>EBN3W2</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>500</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>500</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1024549996</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2003191745</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EBN3W1</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1024465740</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EBN400</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1024465744</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EBN500</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1024465735</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EBN303</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>59.997</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>59.997</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>46196</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1024465733</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2003257391</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2666.26668</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EBN105</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1024575054</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2003203767</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EBN306</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1024465724</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EBN507</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1024465749</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>EBN408</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1024465736</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>EBN309</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>500</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>500</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1024549994</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2003191747</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>9</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>EBN510</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1024465741</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>10</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>EBN311</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1024465751</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>11</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EBN116</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1024575069</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2003202078</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>16</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>EBN316</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1024465752</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>16</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>EBN117</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1024575076</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2003202088</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>17</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>EBN417</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1024465748</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>17</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>EBN418</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1024465756</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>18</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>EBN419</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1024465746</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>19</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>EBN120</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1024575075</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2003202099</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>20</v>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EBN420</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1024465754</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>20</v>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>EBN421</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1024465739</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>21</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>EBN322</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1024465747</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>22</v>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>EBN422</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1024465742</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>22</v>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>EBN423</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1024465728</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>23</v>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>EBN425</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1024465743</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>25</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>EBN326</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>500</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>500</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1024549993</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2003191757</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>26</v>
+      </c>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>EBN127</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1024575065</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2003202120</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>27</v>
+      </c>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>EBN327</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>500</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>500</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1024549998</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2003191751</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>27</v>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>EBN427</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1024465734</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>27</v>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>EBN333</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1024465726</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>33</v>
+      </c>
+      <c r="V45" t="b">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>EBN134</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1024575058</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2003202108</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>34</v>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>EBN434</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1024465727</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>34</v>
+      </c>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>EBN436</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>139.993</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>139.993</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>46206</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1024465767</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2003274184</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>36</v>
+      </c>
+      <c r="V48" t="b">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>6221.288919999999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>EBN538</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1024465755</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>38</v>
+      </c>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>EBN440</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1024465745</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>40</v>
+      </c>
+      <c r="V50" t="b">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>EBN442</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1024465765</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>42</v>
+      </c>
+      <c r="V51" t="b">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>EBN443</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1024465750</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>43</v>
+      </c>
+      <c r="V52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>EBN444</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1024465757</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>44</v>
+      </c>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EBN345</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1024465732</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>45</v>
+      </c>
+      <c r="V54" t="b">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EBN447</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1024465731</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>47</v>
+      </c>
+      <c r="V55" t="b">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EBN449</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1024465763</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>49</v>
+      </c>
+      <c r="V56" t="b">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>EBN553</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1024465730</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>53</v>
+      </c>
+      <c r="V57" t="b">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>EBN156</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>999.152</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>999.152</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1024575063</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2003216281</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>56</v>
+      </c>
+      <c r="V58" t="b">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>12325.4391568</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>EBN559</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1024465738</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>EBN</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>59</v>
+      </c>
+      <c r="V59" t="b">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>EBO1W1</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1024575072</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2003202107</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V60" t="b">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>EBO401</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>500</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>500</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1024549988</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2003191766</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="b">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>EBO303</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>500</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>500</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1024549992</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2003191762</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
+      </c>
+      <c r="V62" t="b">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>EBO109</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1024575066</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2003202074</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>9</v>
+      </c>
+      <c r="V63" t="b">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>EBO517</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>500</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>500</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1024549997</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2003191772</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>17</v>
+      </c>
+      <c r="V64" t="b">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>EBO118</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>750</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>750</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>46167</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1024582759</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2003213267</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>18</v>
+      </c>
+      <c r="V65" t="b">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>EBO519</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>500</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>500</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1024549991</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2003191779</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>19</v>
+      </c>
+      <c r="V66" t="b">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>EBO120</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1024575067</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2003202076</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>20</v>
+      </c>
+      <c r="V67" t="b">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>EBO520</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>300</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>300</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1024549999</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2003191794</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>20</v>
+      </c>
+      <c r="V68" t="b">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>13332</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>EBO521</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>500</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>500</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1024549989</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2003191795</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>21</v>
+      </c>
+      <c r="V69" t="b">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>EBO522</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>500</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>500</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1024549995</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2003191801</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>22</v>
+      </c>
+      <c r="V70" t="b">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2600014698</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>EBO523</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>500</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>500</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>47936</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1024549990</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2003191802</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>23</v>
+      </c>
+      <c r="V71" t="b">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>EBO141</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>750</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>750</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1024582763</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2003213762</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>41</v>
+      </c>
+      <c r="V72" t="b">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>EBO347</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1024465729</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>47</v>
+      </c>
+      <c r="V73" t="b">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>EBO348</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1024465764</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>EBO</t>
+        </is>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>48</v>
+      </c>
+      <c r="V74" t="b">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>EBP3W3</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1024465725</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V75" t="b">
+        <v>1</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>EBP402</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1024465771</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>45</v>
-      </c>
-      <c r="V13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>7.966609999999999</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2545.92142414</v>
+      <c r="V76" t="b">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>EBP303</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1024465772</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3</v>
+      </c>
+      <c r="V77" t="b">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>EBP106</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1024575073</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2003202105</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>6</v>
+      </c>
+      <c r="V78" t="b">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EBP119</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1024575057</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2003202428</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>19</v>
+      </c>
+      <c r="V79" t="b">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>EBP122</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1024575059</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2003202399</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>22</v>
+      </c>
+      <c r="V80" t="b">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>EBP322</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1024465753</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>22</v>
+      </c>
+      <c r="V81" t="b">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>EBP123</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1024575060</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2003202396</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>23</v>
+      </c>
+      <c r="V82" t="b">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>EBP327</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1024465766</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="T83" t="n">
+        <v>3</v>
+      </c>
+      <c r="U83" t="n">
+        <v>27</v>
+      </c>
+      <c r="V83" t="b">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>EBR4W4</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1024465758</v>
+      </c>
+      <c r="R84" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V84" t="b">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GELATINA 200 BLOOM</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2600011176</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>EBR413</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1024465737</v>
+      </c>
+      <c r="R85" t="n">
+        <v>2003234730</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
+      </c>
+      <c r="T85" t="n">
+        <v>4</v>
+      </c>
+      <c r="U85" t="n">
+        <v>13</v>
+      </c>
+      <c r="V85" t="b">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>17775.1112</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>EBS2W1</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>250</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>250</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1024582771</v>
+      </c>
+      <c r="R86" t="n">
+        <v>2003213738</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V86" t="b">
+        <v>1</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>5629.4725</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>EBS102</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>750</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>750</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1024582756</v>
+      </c>
+      <c r="R87" t="n">
+        <v>2003205909</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" t="n">
+        <v>2</v>
+      </c>
+      <c r="V87" t="b">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>EBS106</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>750</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>750</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1024582757</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2003213734</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>6</v>
+      </c>
+      <c r="V88" t="b">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GLICEROL (PC)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2600015715</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>EBS109</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>46886</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1024575064</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2003202265</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
+        <v>9</v>
+      </c>
+      <c r="V89" t="b">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>12.3359</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>12335.9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>EBS114</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>750</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>750</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1024582754</v>
+      </c>
+      <c r="R90" t="n">
+        <v>2003213735</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T90" t="n">
+        <v>1</v>
+      </c>
+      <c r="U90" t="n">
+        <v>14</v>
+      </c>
+      <c r="V90" t="b">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>EBS115</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>750</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>750</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1024582755</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2003213737</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>15</v>
+      </c>
+      <c r="V91" t="b">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>EBS116</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>750</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>750</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1024582770</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2003213736</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>16</v>
+      </c>
+      <c r="V92" t="b">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>EBS117</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>750</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>750</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1024582762</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2003213740</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>17</v>
+      </c>
+      <c r="V93" t="b">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>EBS118</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>750</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>750</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P94" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1024582767</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2003213739</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>18</v>
+      </c>
+      <c r="V94" t="b">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>EBS119</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>750</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>750</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P95" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1024582761</v>
+      </c>
+      <c r="R95" t="n">
+        <v>2003213743</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" t="n">
+        <v>19</v>
+      </c>
+      <c r="V95" t="b">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>EBS120</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>750</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>750</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1024582766</v>
+      </c>
+      <c r="R96" t="n">
+        <v>2003213744</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T96" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" t="n">
+        <v>20</v>
+      </c>
+      <c r="V96" t="b">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>EBS121</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>750</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>750</v>
+      </c>
+      <c r="N97" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P97" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1024582769</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2003213745</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>21</v>
+      </c>
+      <c r="V97" t="b">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>EBS122</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>750</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>750</v>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1024582768</v>
+      </c>
+      <c r="R98" t="n">
+        <v>2003213747</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="n">
+        <v>22</v>
+      </c>
+      <c r="V98" t="b">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>EBS123</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>750</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>750</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1024582764</v>
+      </c>
+      <c r="R99" t="n">
+        <v>2003213760</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>23</v>
+      </c>
+      <c r="V99" t="b">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>EBS124</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>750</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>750</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1024582760</v>
+      </c>
+      <c r="R100" t="n">
+        <v>2003213746</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T100" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" t="n">
+        <v>24</v>
+      </c>
+      <c r="V100" t="b">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>16888.4175</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ACIDO ASCORBICO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2600016047</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>EBS125</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>750</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>750</v>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>47460</v>
+      </c>
+      <c r="P101" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1024582765</v>
+      </c>
+      <c r="R101" t="n">
+        <v>2003213761</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
+        <v>25</v>
+      </c>
+      <c r="V101" t="b">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>22.51789</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>16888.4175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE13"/>
+  <autoFilter ref="A1:AE101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/saida/Documento_Inventario.xlsx
+++ b/data/saida/Documento_Inventario.xlsx
@@ -434,7 +434,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -475,21 +475,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>2000081</v>
+        <v>3001628</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BROMOPRIDA 10MG COM</t>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2617402</t>
+          <t>2600014414</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EBJ245</t>
+          <t>EBI447</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -498,26 +498,26 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>619425</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3000550</v>
+        <v>3001628</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600014414</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>EBM102</t>
+          <t>EBI449</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -526,26 +526,26 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3000550</v>
+        <v>3001628</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600014414</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>EBM103</t>
+          <t>EBI250</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>750</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
@@ -568,12 +568,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>EBM104</t>
+          <t>EBM101</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -587,21 +587,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>EBM108</t>
+          <t>EBM107</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -610,26 +610,26 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>EBM109</t>
+          <t>EBM112</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -638,26 +638,26 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>EBM110</t>
+          <t>EBM115</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -666,26 +666,26 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>EBM111</t>
+          <t>EBM120</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -694,26 +694,26 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EBM113</t>
+          <t>EBM122</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>EBM117</t>
+          <t>EBM124</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -750,26 +750,26 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>EBM118</t>
+          <t>EBM126</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -778,26 +778,26 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>EBM119</t>
+          <t>EBM128</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -806,26 +806,26 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>EBM121</t>
+          <t>EBM130</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -834,26 +834,26 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>EBM123</t>
+          <t>EBM133</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -862,26 +862,26 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>EBM127</t>
+          <t>EBN3W2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -890,26 +890,26 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>EBM134</t>
+          <t>EBN3W1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -918,26 +918,26 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>EBM135</t>
+          <t>EBN400</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,26 +946,26 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>EBM138</t>
+          <t>EBN500</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -974,26 +974,26 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>EBM139</t>
+          <t>EBN303</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1002,26 +1002,26 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>400</v>
+        <v>59.997</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>EBM140</t>
+          <t>EBN105</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1030,26 +1030,26 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>EBM141</t>
+          <t>EBN306</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1058,26 +1058,26 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>EBM142</t>
+          <t>EBN507</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1086,26 +1086,26 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>EBM143</t>
+          <t>EBN408</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1114,26 +1114,26 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>EBM144</t>
+          <t>EBN309</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1142,26 +1142,26 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>399.524</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>EBM145</t>
+          <t>EBN510</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>399.524</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>EBM146</t>
+          <t>EBN311</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1198,26 +1198,26 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3000502</v>
+        <v>3000366</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>EBM148</t>
+          <t>EBN116</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>EBM149</t>
+          <t>EBN316</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1254,26 +1254,26 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>749.874</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>EBM151</t>
+          <t>EBN117</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1282,26 +1282,26 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>EBM154</t>
+          <t>EBN417</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1310,26 +1310,26 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>EBM155</t>
+          <t>EBN418</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1338,26 +1338,26 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>EBM157</t>
+          <t>EBN419</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1366,26 +1366,26 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>EBM158</t>
+          <t>EBN120</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1394,26 +1394,26 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>EBN1W3</t>
+          <t>EBN420</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1422,26 +1422,26 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>EBN1W2</t>
+          <t>EBN421</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1450,26 +1450,26 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>EBN1W1</t>
+          <t>EBN322</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1478,26 +1478,26 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>EBN101</t>
+          <t>EBN422</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1506,26 +1506,26 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2600012493</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>EBN106</t>
+          <t>EBN423</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1534,26 +1534,26 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>EBN107</t>
+          <t>EBN425</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1562,26 +1562,26 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2600012493</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>EBN108</t>
+          <t>EBN326</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>EBN109</t>
+          <t>EBN127</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1618,26 +1618,26 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2600012493</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>EBN110</t>
+          <t>EBN327</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1646,26 +1646,26 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2600012493</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>EBN111</t>
+          <t>EBN427</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1674,26 +1674,26 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>EBN112</t>
+          <t>EBN333</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1702,26 +1702,26 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2600012493</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>EBN113</t>
+          <t>EBN134</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1730,26 +1730,26 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>EBN118</t>
+          <t>EBN434</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1758,26 +1758,26 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>EBN119</t>
+          <t>EBN436</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>750</v>
+        <v>139.993</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>EBN121</t>
+          <t>EBN538</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1814,26 +1814,26 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>EBN122</t>
+          <t>EBN440</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1842,26 +1842,26 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>EBN123</t>
+          <t>EBN442</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1870,26 +1870,26 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>EBN124</t>
+          <t>EBN443</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1898,26 +1898,26 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>EBN224</t>
+          <t>EBN444</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1926,26 +1926,26 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>399.524</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>EBN125</t>
+          <t>EBN345</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1954,26 +1954,26 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>EBN126</t>
+          <t>EBN447</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1982,26 +1982,26 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>EBN131</t>
+          <t>EBN449</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2010,26 +2010,26 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>EBN133</t>
+          <t>EBN553</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2038,26 +2038,26 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>3000502</v>
+        <v>3000366</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>EBN233</t>
+          <t>EBN156</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2066,26 +2066,26 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>399.518</v>
+        <v>999.152</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>EBN135</t>
+          <t>EBN559</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2094,26 +2094,26 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>3000502</v>
+        <v>3000366</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>EBN137</t>
+          <t>EBO1W1</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2122,26 +2122,26 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>EBN138</t>
+          <t>EBO401</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2150,26 +2150,26 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>EBN239</t>
+          <t>EBO303</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2178,26 +2178,26 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>399.524</v>
+        <v>500</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2600016287</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>EBN141</t>
+          <t>EBO109</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2206,26 +2206,26 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>EBN145</t>
+          <t>EBO517</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2234,26 +2234,26 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>3000502</v>
+        <v>3000550</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>EBN146</t>
+          <t>EBO118</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2262,26 +2262,26 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>EBN150</t>
+          <t>EBO519</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2290,26 +2290,26 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>EBN155</t>
+          <t>EBO120</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2318,26 +2318,26 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>EBO1W4</t>
+          <t>EBO520</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2346,26 +2346,26 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>750</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>EBO1W3</t>
+          <t>EBO521</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2374,26 +2374,26 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2600012494</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>EBO100</t>
+          <t>EBO522</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2402,26 +2402,26 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>749.873</v>
+        <v>500</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600014698</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>EBO112</t>
+          <t>EBO523</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row r="72">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>EBO128</t>
+          <t>EBO141</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2463,21 +2463,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>EBO131</t>
+          <t>EBO347</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>EBO132</t>
+          <t>EBO348</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2514,26 +2514,26 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>EBO136</t>
+          <t>EBP3W3</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2542,26 +2542,26 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>EBO138</t>
+          <t>EBP402</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2570,26 +2570,26 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>EBO140</t>
+          <t>EBP303</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2598,26 +2598,26 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>3000502</v>
+        <v>3000366</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>EBO144</t>
+          <t>EBP106</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2626,26 +2626,26 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>3000502</v>
+        <v>3000366</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>EBO145</t>
+          <t>EBP119</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2654,26 +2654,26 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>3000502</v>
+        <v>3000366</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>EBO147</t>
+          <t>EBP122</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2682,26 +2682,26 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>3000502</v>
+        <v>3002233</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>EBO150</t>
+          <t>EBP322</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2710,26 +2710,26 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>400</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>3000502</v>
+        <v>3000366</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>EBO152</t>
+          <t>EBP123</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2738,26 +2738,26 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>EBP1W4</t>
+          <t>EBP327</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2766,26 +2766,26 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>EBP1W3</t>
+          <t>EBR4W4</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2794,26 +2794,26 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>3000550</v>
+        <v>3002233</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GELATINA 200 BLOOM</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600011176</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>EBP1W2</t>
+          <t>EBR413</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>750</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="86">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>EBP1W1</t>
+          <t>EBS2W1</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
     </row>
     <row r="87">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>EBP100</t>
+          <t>EBS102</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>EBP101</t>
+          <t>EBS106</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2911,21 +2911,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>3000550</v>
+        <v>3000366</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>GLICEROL (PC)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600015715</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>EBP102</t>
+          <t>EBS109</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="90">
@@ -2948,12 +2948,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>EBP116</t>
+          <t>EBS114</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>EBP117</t>
+          <t>EBS115</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>2600012581</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>EBP125</t>
+          <t>EBS116</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3023,21 +3023,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>3000502</v>
+        <v>3000550</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>EBP127</t>
+          <t>EBS117</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3046,26 +3046,26 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3000502</v>
+        <v>3000550</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>EBP132</t>
+          <t>EBS118</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3074,26 +3074,26 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>3000502</v>
+        <v>3000550</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>EBP233</t>
+          <t>EBS119</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3102,26 +3102,26 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>399.524</v>
+        <v>750</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>3000502</v>
+        <v>3000550</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>EBP139</t>
+          <t>EBS120</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3130,26 +3130,26 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3000502</v>
+        <v>3000550</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>EBP143</t>
+          <t>EBS121</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3158,26 +3158,26 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3000502</v>
+        <v>3000550</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>EBP145</t>
+          <t>EBS122</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3186,26 +3186,26 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3000502</v>
+        <v>3000550</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>PROPILENOGLICOL</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2600015623</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>EBP148</t>
+          <t>EBS123</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="100">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2600012493</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>EBP557</t>
+          <t>EBS124</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>250</v>
+        <v>750</v>
       </c>
     </row>
     <row r="101">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2600004996</t>
+          <t>2600016047</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>EBP559</t>
+          <t>EBS125</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>249.888</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>

--- a/data/saida/Documento_Inventario.xlsx
+++ b/data/saida/Documento_Inventario.xlsx
@@ -434,7 +434,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -475,21 +475,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3001628</v>
+        <v>2000081</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
+          <t>BROMOPRIDA 10MG COM</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2600014414</t>
+          <t>2617402</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EBI447</t>
+          <t>EBJ245</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -498,26 +498,26 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>600</v>
+        <v>619425</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3001628</v>
+        <v>3000550</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2600014414</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>EBI449</t>
+          <t>EBM102</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -526,26 +526,26 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3001628</v>
+        <v>3000550</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CAP HPMC N.0 BRANCO/BRANCO (AL)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2600014414</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>EBI250</t>
+          <t>EBM103</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>300</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5">
@@ -568,12 +568,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>EBM101</t>
+          <t>EBM104</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -587,21 +587,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>EBM107</t>
+          <t>EBM108</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -610,26 +610,26 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>EBM112</t>
+          <t>EBM109</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -638,26 +638,26 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>EBM115</t>
+          <t>EBM110</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -666,26 +666,26 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>EBM120</t>
+          <t>EBM111</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -694,26 +694,26 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EBM122</t>
+          <t>EBM113</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>EBM124</t>
+          <t>EBM117</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -750,26 +750,26 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>EBM126</t>
+          <t>EBM118</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -778,26 +778,26 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>EBM128</t>
+          <t>EBM119</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -806,26 +806,26 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>EBM130</t>
+          <t>EBM121</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -834,26 +834,26 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>EBM133</t>
+          <t>EBM123</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -862,26 +862,26 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>EBN3W2</t>
+          <t>EBM127</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -890,26 +890,26 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>EBN3W1</t>
+          <t>EBM134</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -918,26 +918,26 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>EBN400</t>
+          <t>EBM135</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,26 +946,26 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>EBN500</t>
+          <t>EBM138</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -974,26 +974,26 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>EBN303</t>
+          <t>EBM139</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1002,26 +1002,26 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>59.997</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>EBN105</t>
+          <t>EBM140</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1030,26 +1030,26 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>EBN306</t>
+          <t>EBM141</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1058,26 +1058,26 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>EBN507</t>
+          <t>EBM142</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1086,26 +1086,26 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>EBN408</t>
+          <t>EBM143</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1114,26 +1114,26 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>EBN309</t>
+          <t>EBM144</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1142,26 +1142,26 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>500</v>
+        <v>399.524</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>EBN510</t>
+          <t>EBM145</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>399.98</v>
+        <v>399.524</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>EBN311</t>
+          <t>EBM146</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1198,26 +1198,26 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3000366</v>
+        <v>3000502</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>EBN116</t>
+          <t>EBM148</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>EBN316</t>
+          <t>EBM149</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1254,26 +1254,26 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>399.98</v>
+        <v>749.874</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>EBN117</t>
+          <t>EBM151</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1282,26 +1282,26 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>EBN417</t>
+          <t>EBM154</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1310,26 +1310,26 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>EBN418</t>
+          <t>EBM155</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1338,26 +1338,26 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>EBN419</t>
+          <t>EBM157</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1366,26 +1366,26 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>EBN120</t>
+          <t>EBM158</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1394,26 +1394,26 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>EBN420</t>
+          <t>EBN1W3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1422,26 +1422,26 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>EBN421</t>
+          <t>EBN1W2</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1450,26 +1450,26 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>EBN322</t>
+          <t>EBN1W1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1478,26 +1478,26 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>EBN422</t>
+          <t>EBN101</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1506,26 +1506,26 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012493</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>EBN423</t>
+          <t>EBN106</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1534,26 +1534,26 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>EBN425</t>
+          <t>EBN107</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1562,26 +1562,26 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600012493</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>EBN326</t>
+          <t>EBN108</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>EBN127</t>
+          <t>EBN109</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1618,26 +1618,26 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600012493</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>EBN327</t>
+          <t>EBN110</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1646,26 +1646,26 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012493</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>EBN427</t>
+          <t>EBN111</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1674,26 +1674,26 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>EBN333</t>
+          <t>EBN112</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1702,26 +1702,26 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012493</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>EBN134</t>
+          <t>EBN113</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1730,26 +1730,26 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>EBN434</t>
+          <t>EBN118</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1758,26 +1758,26 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>EBN436</t>
+          <t>EBN119</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>139.993</v>
+        <v>750</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>EBN538</t>
+          <t>EBN121</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1814,26 +1814,26 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>EBN440</t>
+          <t>EBN122</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1842,26 +1842,26 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>EBN442</t>
+          <t>EBN123</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1870,26 +1870,26 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>EBN443</t>
+          <t>EBN124</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1898,26 +1898,26 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>EBN444</t>
+          <t>EBN224</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1926,26 +1926,26 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>399.98</v>
+        <v>399.524</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>EBN345</t>
+          <t>EBN125</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1954,26 +1954,26 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>EBN447</t>
+          <t>EBN126</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1982,26 +1982,26 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>EBN449</t>
+          <t>EBN131</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2010,26 +2010,26 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>EBN553</t>
+          <t>EBN133</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2038,26 +2038,26 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>3000366</v>
+        <v>3000502</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>EBN156</t>
+          <t>EBN233</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2066,26 +2066,26 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>999.152</v>
+        <v>399.518</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>EBN559</t>
+          <t>EBN135</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2094,26 +2094,26 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>3000366</v>
+        <v>3000502</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>EBO1W1</t>
+          <t>EBN137</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2122,26 +2122,26 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>EBO401</t>
+          <t>EBN138</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2150,26 +2150,26 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>EBO303</t>
+          <t>EBN239</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2178,26 +2178,26 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>500</v>
+        <v>399.524</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600016287</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>EBO109</t>
+          <t>EBN141</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2206,26 +2206,26 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>EBO517</t>
+          <t>EBN145</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2234,26 +2234,26 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>3000550</v>
+        <v>3000502</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>EBO118</t>
+          <t>EBN146</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2262,26 +2262,26 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>EBO519</t>
+          <t>EBN150</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2290,26 +2290,26 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>EBO120</t>
+          <t>EBN155</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2318,26 +2318,26 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>EBO520</t>
+          <t>EBO1W4</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2346,26 +2346,26 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>300</v>
+        <v>750</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>EBO521</t>
+          <t>EBO1W3</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2374,26 +2374,26 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600012494</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>EBO522</t>
+          <t>EBO100</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2402,26 +2402,26 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>500</v>
+        <v>749.873</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2600014698</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>EBO523</t>
+          <t>EBO112</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row r="72">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>EBO141</t>
+          <t>EBO128</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2463,21 +2463,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>EBO347</t>
+          <t>EBO131</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>EBO348</t>
+          <t>EBO132</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2514,26 +2514,26 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>EBP3W3</t>
+          <t>EBO136</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2542,26 +2542,26 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>EBP402</t>
+          <t>EBO138</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2570,26 +2570,26 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>EBP303</t>
+          <t>EBO140</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2598,26 +2598,26 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>3000366</v>
+        <v>3000502</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>EBP106</t>
+          <t>EBO144</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2626,26 +2626,26 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>3000366</v>
+        <v>3000502</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>EBP119</t>
+          <t>EBO145</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2654,26 +2654,26 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>3000366</v>
+        <v>3000502</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>EBP122</t>
+          <t>EBO147</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2682,26 +2682,26 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>3002233</v>
+        <v>3000502</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>EBP322</t>
+          <t>EBO150</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2710,26 +2710,26 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>399.98</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>3000366</v>
+        <v>3000502</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>EBP123</t>
+          <t>EBO152</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2738,26 +2738,26 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>EBP327</t>
+          <t>EBP1W4</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2766,26 +2766,26 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>EBR4W4</t>
+          <t>EBP1W3</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2794,26 +2794,26 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>3002233</v>
+        <v>3000550</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>GELATINA 200 BLOOM</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>2600011176</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>EBR413</t>
+          <t>EBP1W2</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>399.98</v>
+        <v>750</v>
       </c>
     </row>
     <row r="86">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>EBS2W1</t>
+          <t>EBP1W1</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>250</v>
+        <v>750</v>
       </c>
     </row>
     <row r="87">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>EBS102</t>
+          <t>EBP100</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>EBS106</t>
+          <t>EBP101</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2911,21 +2911,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>3000366</v>
+        <v>3000550</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>GLICEROL (PC)</t>
+          <t>ACIDO ASCORBICO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2600015715</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>EBS109</t>
+          <t>EBP102</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="90">
@@ -2948,12 +2948,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>EBS114</t>
+          <t>EBP116</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>EBS115</t>
+          <t>EBP117</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600012581</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>EBS116</t>
+          <t>EBP125</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3023,21 +3023,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>3000550</v>
+        <v>3000502</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>EBS117</t>
+          <t>EBP127</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3046,26 +3046,26 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3000550</v>
+        <v>3000502</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>EBS118</t>
+          <t>EBP132</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3074,26 +3074,26 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>3000550</v>
+        <v>3000502</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>EBS119</t>
+          <t>EBP233</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3102,26 +3102,26 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>750</v>
+        <v>399.524</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>3000550</v>
+        <v>3000502</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>EBS120</t>
+          <t>EBP139</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3130,26 +3130,26 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3000550</v>
+        <v>3000502</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>EBS121</t>
+          <t>EBP143</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3158,26 +3158,26 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3000550</v>
+        <v>3000502</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>EBS122</t>
+          <t>EBP145</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3186,26 +3186,26 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3000550</v>
+        <v>3000502</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>ACIDO ASCORBICO</t>
+          <t>PROPILENOGLICOL</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600015623</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>EBS123</t>
+          <t>EBP148</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row r="100">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600012493</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>EBS124</t>
+          <t>EBP557</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2600016047</t>
+          <t>2600004996</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>EBS125</t>
+          <t>EBP559</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>750</v>
+        <v>249.888</v>
       </c>
     </row>
   </sheetData>
